--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/MISSOURI_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/MISSOURI_2024.xlsx
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C163">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C253">
